--- a/data/VitaminD/stockton2011/stockton2011_vitamind_muscle_strength.xlsx
+++ b/data/VitaminD/stockton2011/stockton2011_vitamind_muscle_strength.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Author</t>
   </si>
@@ -89,7 +89,7 @@
     <t>Gradyb</t>
   </si>
   <si>
-    <t>SMD</t>
+    <t>d</t>
   </si>
   <si>
     <t>J</t>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>se_g</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>n not available, d used</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF761A1-502D-49C2-8946-F37011FFEE87}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -438,7 +444,7 @@
     <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,8 +478,11 @@
       <c r="K1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -510,6 +519,9 @@
       <c r="K2">
         <f>I2*G2</f>
         <v>0.24843423799582465</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
